--- a/doc/部署/点位信息.xlsx
+++ b/doc/部署/点位信息.xlsx
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:12">
+    <row r="2" spans="1:12">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="8">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>15</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="J2" s="10"/>
     </row>
-    <row r="3" ht="14.25" hidden="1" spans="1:12">
+    <row r="3" ht="14.25" spans="1:12">
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="14.25" hidden="1" spans="1:12">
+    <row r="4" ht="14.25" spans="1:12">
       <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" ht="14.25" hidden="1" spans="1:12">
+    <row r="5" ht="14.25" spans="1:12">
       <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="14.25" hidden="1" spans="1:12">
+    <row r="6" ht="14.25" spans="1:12">
       <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="14.25" hidden="1" spans="1:12">
+    <row r="7" ht="14.25" spans="1:12">
       <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" ht="14.25" hidden="1" spans="1:12">
+    <row r="8" ht="14.25" spans="1:12">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" ht="14.25" hidden="1" spans="1:12">
+    <row r="9" ht="14.25" spans="1:12">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" ht="14.25" hidden="1" spans="1:12">
+    <row r="10" ht="14.25" spans="1:12">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" ht="14.25" hidden="1" spans="1:12">
+    <row r="11" ht="14.25" spans="1:12">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" ht="14.25" hidden="1" spans="1:12">
+    <row r="12" ht="14.25" spans="1:12">
       <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" ht="14.25" hidden="1" spans="1:12">
+    <row r="13" ht="14.25" spans="1:12">
       <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" ht="14.25" hidden="1" spans="1:12">
+    <row r="14" ht="14.25" spans="1:12">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" ht="14.25" hidden="1" spans="1:12">
+    <row r="15" ht="14.25" spans="1:12">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="16" ht="14.25" hidden="1" spans="1:12">
+    <row r="16" ht="14.25" spans="1:12">
       <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="17" ht="14.25" hidden="1" spans="1:12">
+    <row r="17" ht="14.25" spans="1:12">
       <c r="A17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="18" ht="14.25" hidden="1" spans="1:12">
+    <row r="18" ht="14.25" spans="1:12">
       <c r="A18" s="7" t="s">
         <v>11</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" ht="14.25" hidden="1" spans="1:12">
+    <row r="19" ht="14.25" spans="1:12">
       <c r="A19" s="7" t="s">
         <v>11</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" ht="14.25" hidden="1" spans="1:12">
+    <row r="20" ht="14.25" spans="1:12">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="21" ht="14.25" hidden="1" spans="1:12">
+    <row r="21" ht="14.25" spans="1:12">
       <c r="A21" s="7" t="s">
         <v>11</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" ht="14.25" hidden="1" spans="1:12">
+    <row r="22" ht="14.25" spans="1:12">
       <c r="A22" s="7" t="s">
         <v>11</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="23" ht="14.25" hidden="1" spans="1:12">
+    <row r="23" ht="14.25" spans="1:12">
       <c r="A23" s="7" t="s">
         <v>11</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="24" ht="14.25" hidden="1" spans="1:12">
+    <row r="24" ht="14.25" spans="1:12">
       <c r="A24" s="7" t="s">
         <v>11</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="25" ht="14.25" hidden="1" spans="1:12">
+    <row r="25" ht="14.25" spans="1:12">
       <c r="A25" s="7" t="s">
         <v>11</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="26" ht="14.25" hidden="1" spans="1:12">
+    <row r="26" ht="14.25" spans="1:12">
       <c r="A26" s="7" t="s">
         <v>11</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="27" ht="14.25" hidden="1" spans="1:12">
+    <row r="27" ht="14.25" spans="1:12">
       <c r="A27" s="7" t="s">
         <v>11</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="28" ht="14.25" hidden="1" spans="1:12">
+    <row r="28" ht="14.25" spans="1:12">
       <c r="A28" s="7" t="s">
         <v>11</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" ht="14.25" hidden="1" spans="1:12">
+    <row r="29" ht="14.25" spans="1:12">
       <c r="A29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="30" ht="14.25" hidden="1" spans="1:12">
+    <row r="30" ht="14.25" spans="1:12">
       <c r="A30" s="7" t="s">
         <v>11</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="31" ht="14.25" hidden="1" spans="1:12">
+    <row r="31" ht="14.25" spans="1:12">
       <c r="A31" s="7" t="s">
         <v>11</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" ht="14.25" hidden="1" spans="1:12">
+    <row r="32" ht="14.25" spans="1:12">
       <c r="A32" s="7" t="s">
         <v>11</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="33" ht="14.25" hidden="1" spans="1:15">
+    <row r="33" ht="14.25" spans="1:15">
       <c r="A33" s="7" t="s">
         <v>11</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="14.25" hidden="1" spans="1:15">
+    <row r="34" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A34" s="13" t="s">
         <v>11</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>14</v>
       </c>
       <c r="G34" s="8">
-        <v>2501</v>
+        <v>3301</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>15</v>
@@ -2449,7 +2449,7 @@
       <c r="J34" s="15"/>
       <c r="L34" s="16"/>
     </row>
-    <row r="35" ht="14.25" hidden="1" spans="1:15">
+    <row r="35" ht="14.25" spans="1:15">
       <c r="A35" s="7" t="s">
         <v>11</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="36" ht="14.25" hidden="1" spans="1:15">
+    <row r="36" ht="14.25" spans="1:15">
       <c r="A36" s="7" t="s">
         <v>11</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="37" ht="14.25" hidden="1" spans="1:15">
+    <row r="37" ht="14.25" spans="1:15">
       <c r="A37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" ht="14.25" hidden="1" spans="1:15">
+    <row r="38" ht="14.25" spans="1:15">
       <c r="A38" s="7" t="s">
         <v>11</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" ht="14.25" hidden="1" spans="1:15">
+    <row r="39" ht="14.25" spans="1:15">
       <c r="A39" s="7" t="s">
         <v>11</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" ht="14.25" hidden="1" spans="1:15">
+    <row r="40" ht="14.25" spans="1:15">
       <c r="A40" s="7" t="s">
         <v>11</v>
       </c>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="J40" s="10"/>
     </row>
-    <row r="41" s="1" customFormat="1" ht="14.25" hidden="1" spans="1:15">
+    <row r="41" s="1" customFormat="1" ht="14.25" spans="1:15">
       <c r="A41" s="13" t="s">
         <v>11</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" s="2" customFormat="1" spans="1:15">
+    <row r="42" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:15">
       <c r="A42" s="8" t="s">
         <v>65</v>
       </c>
@@ -2700,7 +2700,7 @@
       <c r="J42" s="10"/>
       <c r="L42" s="12"/>
     </row>
-    <row r="43" ht="14.25" spans="1:15">
+    <row r="43" ht="14.25" hidden="1" spans="1:15">
       <c r="A43" s="8" t="s">
         <v>65</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" ht="14.25" spans="1:15">
+    <row r="44" ht="14.25" hidden="1" spans="1:15">
       <c r="A44" s="8" t="s">
         <v>65</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" ht="14.25" spans="1:15">
+    <row r="45" ht="14.25" hidden="1" spans="1:15">
       <c r="A45" s="8" t="s">
         <v>65</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" ht="14.25" spans="1:15">
+    <row r="46" ht="14.25" hidden="1" spans="1:15">
       <c r="A46" s="8" t="s">
         <v>65</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="47" ht="14.25" spans="1:15">
+    <row r="47" ht="14.25" hidden="1" spans="1:15">
       <c r="A47" s="8" t="s">
         <v>65</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="48" ht="14.25" spans="1:15">
+    <row r="48" ht="14.25" hidden="1" spans="1:15">
       <c r="A48" s="8" t="s">
         <v>65</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="49" ht="14.25" spans="1:12">
+    <row r="49" ht="14.25" hidden="1" spans="1:12">
       <c r="A49" s="8" t="s">
         <v>65</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="50" ht="14.25" spans="1:12">
+    <row r="50" ht="14.25" hidden="1" spans="1:12">
       <c r="A50" s="8" t="s">
         <v>65</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" ht="14.25" spans="1:12">
+    <row r="51" ht="14.25" hidden="1" spans="1:12">
       <c r="A51" s="8" t="s">
         <v>65</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" ht="14.25" spans="1:12">
+    <row r="52" ht="14.25" hidden="1" spans="1:12">
       <c r="A52" s="8" t="s">
         <v>65</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" ht="14.25" spans="1:12">
+    <row r="53" ht="14.25" hidden="1" spans="1:12">
       <c r="A53" s="8" t="s">
         <v>65</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="54" ht="14.25" spans="1:12">
+    <row r="54" ht="14.25" hidden="1" spans="1:12">
       <c r="A54" s="8" t="s">
         <v>65</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="55" ht="14.25" spans="1:12">
+    <row r="55" ht="14.25" hidden="1" spans="1:12">
       <c r="A55" s="8" t="s">
         <v>65</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="56" ht="14.25" spans="1:12">
+    <row r="56" ht="14.25" hidden="1" spans="1:12">
       <c r="A56" s="8" t="s">
         <v>65</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" ht="14.25" spans="1:12">
+    <row r="57" ht="14.25" hidden="1" spans="1:12">
       <c r="A57" s="8" t="s">
         <v>65</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="58" ht="14.25" spans="1:12">
+    <row r="58" ht="14.25" hidden="1" spans="1:12">
       <c r="A58" s="8" t="s">
         <v>65</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="59" ht="14.25" spans="1:12">
+    <row r="59" ht="14.25" hidden="1" spans="1:12">
       <c r="A59" s="8" t="s">
         <v>65</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="60" ht="14.25" spans="1:12">
+    <row r="60" ht="14.25" hidden="1" spans="1:12">
       <c r="A60" s="20" t="s">
         <v>65</v>
       </c>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="J60" s="18"/>
     </row>
-    <row r="61" ht="14.25" spans="1:12">
+    <row r="61" ht="14.25" hidden="1" spans="1:12">
       <c r="A61" s="8" t="s">
         <v>65</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" ht="14.25" spans="1:12">
+    <row r="62" ht="14.25" hidden="1" spans="1:12">
       <c r="A62" s="8" t="s">
         <v>65</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" ht="14.25" spans="1:12">
+    <row r="63" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:12">
       <c r="A63" s="8" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3397,9 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O63" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <filters>
-        <filter val="A线"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="B线"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>
